--- a/examples/sample_before.xlsx
+++ b/examples/sample_before.xlsx
@@ -5,6 +5,7 @@
   <sheets>
     <sheet name="Revenue build" sheetId="1" r:id="rId1"/>
     <sheet name="Operating costs" sheetId="2" r:id="rId2"/>
+    <sheet name="Prior year" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -515,9 +516,35 @@
         <v>23400</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Cohorts</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Revenue per cohort</v>
+      </c>
+      <c r="B14">
+        <f>B9/B13</f>
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Prior year revenue</v>
+      </c>
+      <c r="B16">
+        <f>'Prior year'!B9</f>
+        <v>24000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -625,4 +652,30 @@
     <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Prior year</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Revenue</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9">
+        <v>24000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/examples/sample_before.xlsx
+++ b/examples/sample_before.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -542,9 +542,41 @@
         <v>24000</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Monthly ramp</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19">
+        <f>B18*1.01</f>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20">
+        <f>B19*1.01</f>
+        <v>102.01</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21">
+        <f>B20*1.01</f>
+        <v>103.0301</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22">
+        <f>B21*1.01</f>
+        <v>104.060401</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/examples/sample_before.xlsx
+++ b/examples/sample_before.xlsx
@@ -7,6 +7,11 @@
     <sheet name="Operating costs" sheetId="2" r:id="rId2"/>
     <sheet name="Prior year" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="GrowthRate">'Revenue build'!$B$4</definedName>
+    <definedName name="TAX1">'Revenue build'!$B$24</definedName>
+    <definedName name="LegacyOpex">'Operating costs'!$B$7</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -399,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -574,16 +579,24 @@
         <v>104.060401</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Tax rate</v>
+      </c>
+      <c r="B24">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -679,9 +692,30 @@
         <v>611</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>After tax</v>
+      </c>
+      <c r="B8">
+        <f>B7*TAX1</f>
+        <v>114</v>
+      </c>
+      <c r="C8">
+        <f>C7*TAX1</f>
+        <v>116.4</v>
+      </c>
+      <c r="D8">
+        <f>D7*TAX1</f>
+        <v>119.80000000000001</v>
+      </c>
+      <c r="E8">
+        <f>E7*TAX1</f>
+        <v>122.2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
   </ignoredErrors>
 </worksheet>
 </file>
